--- a/MidWest_Precision_FP&A_Model.xlsx
+++ b/MidWest_Precision_FP&A_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manasigawade/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8674D524-861E-F046-8038-9FBB6FF44A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E57B5B-81F0-6D4F-8A30-19F53A024528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" firstSheet="11" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4500" yWindow="600" windowWidth="29400" windowHeight="16980" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -35,14 +35,15 @@
     <sheet name="Scenario_Analysis" sheetId="19" r:id="rId20"/>
     <sheet name="Variance_Drivers" sheetId="20" r:id="rId21"/>
     <sheet name="Management_Dashboard" sheetId="21" r:id="rId22"/>
-    <sheet name="Checks" sheetId="22" r:id="rId23"/>
+    <sheet name="Executive_Dashboard" sheetId="24" r:id="rId23"/>
+    <sheet name="Checks" sheetId="22" r:id="rId24"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId24"/>
+    <externalReference r:id="rId25"/>
   </externalReferences>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId25"/>
+    <pivotCache cacheId="9" r:id="rId26"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -55,7 +56,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="351">
   <si>
     <t>MidWest Precision Components, Inc.</t>
   </si>
@@ -1060,13 +1060,73 @@
   </si>
   <si>
     <t>Sum of 2028 Revenue</t>
+  </si>
+  <si>
+    <t>MIDWEST PRECISION COMPONENTS  |  FP&amp;A</t>
+  </si>
+  <si>
+    <t>EXECUTIVE FINANCIAL DASHBOARD  •  2026 FORECAST  •  INDEPENDENT PORTFOLIO PROJECT</t>
+  </si>
+  <si>
+    <t>REVENUE</t>
+  </si>
+  <si>
+    <t>GROSS MARGIN</t>
+  </si>
+  <si>
+    <t>EBITDA MARGIN</t>
+  </si>
+  <si>
+    <t>NET INCOME</t>
+  </si>
+  <si>
+    <t>ENDING CASH</t>
+  </si>
+  <si>
+    <t>CAPACITY UTILIZATION</t>
+  </si>
+  <si>
+    <t>REVENUE TREND  |  $ MILLIONS</t>
+  </si>
+  <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Revenue ($M)</t>
+  </si>
+  <si>
+    <t>2025 Actual</t>
+  </si>
+  <si>
+    <t>BUDGET VS. FORECAST  |  2026</t>
+  </si>
+  <si>
+    <t>Variance (F - B)</t>
+  </si>
+  <si>
+    <t>EBITDA Margin</t>
+  </si>
+  <si>
+    <t>Net Income ($M)</t>
+  </si>
+  <si>
+    <t>Ending Cash ($M)</t>
+  </si>
+  <si>
+    <t>MODEL NOTES</t>
+  </si>
+  <si>
+    <t>All KPIs and comparison values link to Management_Dashboard; no financial figures are manually entered here.</t>
+  </si>
+  <si>
+    <t>Scenario selection and source-model integrity should be verified before sharing externally.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="10">
+  <numFmts count="13">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
@@ -1077,8 +1137,11 @@
     <numFmt numFmtId="167" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="_(&quot;$&quot;* #,##0.0_);_(&quot;$&quot;* \(#,##0.0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="169" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="\$0.00,,&quot;M&quot;"/>
+    <numFmt numFmtId="171" formatCode="0.00;[Red]\(0.00\);\-"/>
+    <numFmt numFmtId="172" formatCode="0.0%;[Red]\(0.0%\);\-"/>
   </numFmts>
-  <fonts count="46" x14ac:knownFonts="1">
+  <fonts count="61">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1407,8 +1470,105 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF65758B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF65758B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF65758B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="21"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF65758B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1436,6 +1596,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1473,7 +1645,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1640,6 +1812,47 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="52" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="54" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="57" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="59" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="58" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="59" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="58" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="59" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2791,6 +3004,543 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.2080087028595116E-2"/>
+          <c:y val="5.9427703369876191E-2"/>
+          <c:w val="0.93476201823456273"/>
+          <c:h val="0.84504929488315572"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Revenue ($M)</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>2025 Actual</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2026 Budget</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>2026 Forecast</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>2027 Plan</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>2028 Plan</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>0.00;[Red]\(0.00\);\-</c:formatCode>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>49.95</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>52.991954999999997</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>52.478718749999985</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>56.489424030000002</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>57.901659630749982</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-922A-A846-B846-265D110E68FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00;[Red]\(0.00\);\-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.2080087028595116E-2"/>
+          <c:y val="5.9427703369876191E-2"/>
+          <c:w val="0.93476201823456273"/>
+          <c:h val="0.84504929488315572"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Revenue ($M)</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>[1]Executive_Dashboard!$D$16:$D$20</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2025 Actual</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2026 Budget</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2026 Forecast</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2027 Plan</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2028 Plan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[1]Executive_Dashboard!$E$16:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.00;[Red]\(0.00\);\-</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>49.95</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52.991954999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>52.478718749999985</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>56.489424030000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>57.901659630749982</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4C06-4542-AE6E-DC1ECFCA52C0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00;[Red]\(0.00\);\-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.2080087028595116E-2"/>
+          <c:y val="5.9427703369876191E-2"/>
+          <c:w val="0.93476201823456273"/>
+          <c:h val="0.84504929488315572"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Revenue ($M)</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>[1]Executive_Dashboard!$D$16:$D$20</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2025 Actual</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2026 Budget</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2026 Forecast</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2027 Plan</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2028 Plan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[1]Executive_Dashboard!$E$16:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.00;[Red]\(0.00\);\-</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>49.95</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52.991954999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>52.478718749999985</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>56.489424030000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>57.901659630749982</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B0A1-A04A-80B7-78DC200C2D95}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00;[Red]\(0.00\);\-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -3375,6 +4125,125 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>158750</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>317499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>285750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{549521D7-CC56-7249-AA7B-E348A2E9DD06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>158750</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>317499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>285750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{040F69F5-D424-BB46-90E9-C7AD6EC2A975}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>158750</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>317499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>285750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F43CB77-9F3B-C74F-BF8E-42FA402B78C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -3383,6 +4252,7 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
+      <sheetName val="Dashboard"/>
       <sheetName val="Control Panel"/>
       <sheetName val="Historical_Actuals"/>
       <sheetName val="Assumptions"/>
@@ -3404,6 +4274,7 @@
       <sheetName val="Variance_Drivers"/>
       <sheetName val="Management_Dashboard"/>
       <sheetName val="Checks"/>
+      <sheetName val="Executive_Dashboard"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -3411,23 +4282,7 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>Precision Components</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>Industrial Assemblies</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>Automotive Components</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
@@ -3444,6 +4299,49 @@
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23">
+        <row r="16">
+          <cell r="D16" t="str">
+            <v>2025 Actual</v>
+          </cell>
+          <cell r="E16">
+            <v>49.95</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="D17" t="str">
+            <v>2026 Budget</v>
+          </cell>
+          <cell r="E17">
+            <v>52.991954999999997</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="D18" t="str">
+            <v>2026 Forecast</v>
+          </cell>
+          <cell r="E18">
+            <v>52.478718749999985</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="D19" t="str">
+            <v>2027 Plan</v>
+          </cell>
+          <cell r="E19">
+            <v>56.489424030000002</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="D20" t="str">
+            <v>2028 Plan</v>
+          </cell>
+          <cell r="E20">
+            <v>57.901659630749982</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3576,7 +4474,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A71CC6CB-E758-674C-B8AC-B9E1A351A079}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A71CC6CB-E758-674C-B8AC-B9E1A351A079}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A1:F5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField axis="axisRow" showAll="0">
@@ -4004,7 +4902,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="3"/>
     <col min="2" max="2" width="41" style="3" customWidth="1"/>
@@ -4013,7 +4911,7 @@
     <col min="9" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" ht="31">
       <c r="B2" s="116" t="s">
         <v>0</v>
       </c>
@@ -4024,7 +4922,7 @@
       <c r="G2" s="116"/>
       <c r="H2" s="116"/>
     </row>
-    <row r="3" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" ht="19">
       <c r="B3" s="117" t="s">
         <v>280</v>
       </c>
@@ -4035,7 +4933,7 @@
       <c r="G3" s="117"/>
       <c r="H3" s="117"/>
     </row>
-    <row r="6" spans="2:8" ht="21" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" ht="21">
       <c r="B6" s="118" t="s">
         <v>281</v>
       </c>
@@ -4046,7 +4944,7 @@
       <c r="G6" s="118"/>
       <c r="H6" s="118"/>
     </row>
-    <row r="7" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" ht="19">
       <c r="B7" s="4" t="s">
         <v>282</v>
       </c>
@@ -4059,7 +4957,7 @@
       <c r="G7" s="115"/>
       <c r="H7" s="115"/>
     </row>
-    <row r="8" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" ht="19">
       <c r="B8" s="4" t="s">
         <v>284</v>
       </c>
@@ -4072,7 +4970,7 @@
       <c r="G8" s="115"/>
       <c r="H8" s="115"/>
     </row>
-    <row r="9" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="19">
       <c r="B9" s="4" t="s">
         <v>286</v>
       </c>
@@ -4085,7 +4983,7 @@
       <c r="G9" s="115"/>
       <c r="H9" s="115"/>
     </row>
-    <row r="10" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" ht="19">
       <c r="B10" s="4" t="s">
         <v>288</v>
       </c>
@@ -4098,7 +4996,7 @@
       <c r="G10" s="115"/>
       <c r="H10" s="115"/>
     </row>
-    <row r="11" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="19">
       <c r="B11" s="4" t="s">
         <v>290</v>
       </c>
@@ -4111,7 +5009,7 @@
       <c r="G11" s="115"/>
       <c r="H11" s="115"/>
     </row>
-    <row r="12" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" ht="19">
       <c r="B12" s="4" t="s">
         <v>292</v>
       </c>
@@ -4124,7 +5022,7 @@
       <c r="G12" s="115"/>
       <c r="H12" s="115"/>
     </row>
-    <row r="13" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" ht="19">
       <c r="B13" s="4" t="s">
         <v>294</v>
       </c>
@@ -4137,7 +5035,7 @@
       <c r="G13" s="115"/>
       <c r="H13" s="115"/>
     </row>
-    <row r="14" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="19">
       <c r="B14" s="4" t="s">
         <v>296</v>
       </c>
@@ -4150,7 +5048,7 @@
       <c r="G14" s="115"/>
       <c r="H14" s="115"/>
     </row>
-    <row r="15" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" ht="19">
       <c r="B15" s="4" t="s">
         <v>298</v>
       </c>
@@ -4163,7 +5061,7 @@
       <c r="G15" s="115"/>
       <c r="H15" s="115"/>
     </row>
-    <row r="16" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" ht="19">
       <c r="B16" s="4" t="s">
         <v>300</v>
       </c>
@@ -4176,7 +5074,7 @@
       <c r="G16" s="115"/>
       <c r="H16" s="115"/>
     </row>
-    <row r="17" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" ht="19">
       <c r="B17" s="4" t="s">
         <v>302</v>
       </c>
@@ -4189,7 +5087,7 @@
       <c r="G17" s="115"/>
       <c r="H17" s="115"/>
     </row>
-    <row r="18" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" ht="19">
       <c r="B18" s="4" t="s">
         <v>304</v>
       </c>
@@ -4202,7 +5100,7 @@
       <c r="G18" s="115"/>
       <c r="H18" s="115"/>
     </row>
-    <row r="19" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" ht="19">
       <c r="B19" s="4" t="s">
         <v>306</v>
       </c>
@@ -4215,7 +5113,7 @@
       <c r="G19" s="115"/>
       <c r="H19" s="115"/>
     </row>
-    <row r="20" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" ht="19">
       <c r="B20" s="4" t="s">
         <v>308</v>
       </c>
@@ -4255,7 +5153,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{056DA7DB-D10E-4411-B924-41585833FD1B}">
   <dimension ref="A1:Q8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
@@ -4276,17 +5174,17 @@
     <col min="18" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="19">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" ht="16">
       <c r="A2" s="7" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17">
       <c r="A4" s="18" t="s">
         <v>35</v>
       </c>
@@ -4339,7 +5237,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17">
       <c r="A5" s="3" t="s">
         <v>48</v>
       </c>
@@ -4406,7 +5304,7 @@
         <v>1631213.5550156753</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17">
       <c r="A6" s="3" t="s">
         <v>49</v>
       </c>
@@ -4473,7 +5371,7 @@
         <v>1622891.0368778403</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="16" thickBot="1">
       <c r="A7" s="3" t="s">
         <v>50</v>
       </c>
@@ -4540,7 +5438,7 @@
         <v>1122291.5708870604</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17">
       <c r="A8" s="38" t="s">
         <v>107</v>
       </c>
@@ -4590,7 +5488,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E03D86B6-0BD5-423D-83D9-BE0A38F0A66D}">
   <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.5" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" style="3"/>
@@ -4599,17 +5497,17 @@
     <col min="8" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="19">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="16">
       <c r="A2" s="7" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9">
       <c r="A4" s="18" t="s">
         <v>108</v>
       </c>
@@ -4638,7 +5536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5" s="3" t="s">
         <v>111</v>
       </c>
@@ -4671,7 +5569,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9">
       <c r="A6" s="3" t="s">
         <v>112</v>
       </c>
@@ -4701,7 +5599,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9">
       <c r="A7" s="3" t="s">
         <v>113</v>
       </c>
@@ -4731,7 +5629,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9">
       <c r="A8" s="3" t="s">
         <v>118</v>
       </c>
@@ -4761,7 +5659,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="16" thickBot="1">
       <c r="A9" s="3" t="s">
         <v>119</v>
       </c>
@@ -4791,7 +5689,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10" s="38" t="s">
         <v>121</v>
       </c>
@@ -4817,7 +5715,7 @@
         <v>3943733.3047853564</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9">
       <c r="A12" s="64" t="s">
         <v>89</v>
       </c>
@@ -4828,7 +5726,7 @@
       <c r="F12" s="64"/>
       <c r="G12" s="64"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9">
       <c r="A13" s="3" t="s">
         <v>123</v>
       </c>
@@ -4848,7 +5746,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9">
       <c r="A14" s="3" t="s">
         <v>124</v>
       </c>
@@ -4873,7 +5771,7 @@
         <v>307529.23953664128</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9">
       <c r="A15" s="3" t="s">
         <v>125</v>
       </c>
@@ -4909,7 +5807,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEE46F4-8C35-4817-AF70-4B8FC4610524}">
   <dimension ref="A1:O12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17" style="3" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" style="3"/>
@@ -4922,17 +5820,17 @@
     <col min="16" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="19">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="16">
       <c r="A2" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15">
       <c r="A5" s="18" t="s">
         <v>126</v>
       </c>
@@ -4979,7 +5877,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15">
       <c r="A6" s="3" t="s">
         <v>141</v>
       </c>
@@ -5034,7 +5932,7 @@
         <v>946962.89999999991</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15">
       <c r="A7" s="3" t="s">
         <v>142</v>
       </c>
@@ -5089,7 +5987,7 @@
         <v>1303466.58</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15">
       <c r="A8" s="3" t="s">
         <v>143</v>
       </c>
@@ -5144,7 +6042,7 @@
         <v>1764693.2159999995</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15">
       <c r="A9" s="3" t="s">
         <v>144</v>
       </c>
@@ -5199,7 +6097,7 @@
         <v>1375881.3899999997</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15">
       <c r="A10" s="3" t="s">
         <v>145</v>
       </c>
@@ -5254,7 +6152,7 @@
         <v>606056.25599999994</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="16" thickBot="1">
       <c r="A11" s="3" t="s">
         <v>146</v>
       </c>
@@ -5309,7 +6207,7 @@
         <v>686269.58399999992</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" s="27" customFormat="1">
       <c r="A12" s="38" t="s">
         <v>147</v>
       </c>
@@ -5383,7 +6281,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{731B6D8B-825F-43A5-83DF-793B6D02E471}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
@@ -5392,17 +6290,17 @@
     <col min="7" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="19">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="16">
       <c r="A2" s="7" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="18" t="s">
         <v>148</v>
       </c>
@@ -5425,7 +6323,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="3" t="s">
         <v>142</v>
       </c>
@@ -5452,7 +6350,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="3" t="s">
         <v>149</v>
       </c>
@@ -5479,7 +6377,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="3" t="s">
         <v>150</v>
       </c>
@@ -5506,7 +6404,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="3" t="s">
         <v>151</v>
       </c>
@@ -5533,7 +6431,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="3" t="s">
         <v>152</v>
       </c>
@@ -5560,7 +6458,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="3" t="s">
         <v>153</v>
       </c>
@@ -5587,7 +6485,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16" thickBot="1">
       <c r="A11" s="3" t="s">
         <v>154</v>
       </c>
@@ -5614,7 +6512,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="38" t="s">
         <v>157</v>
       </c>
@@ -5652,7 +6550,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C595D092-3E62-4548-9CB8-6B819CAFD971}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.6640625" style="3" customWidth="1"/>
     <col min="2" max="2" width="16" style="3" customWidth="1"/>
@@ -5664,17 +6562,17 @@
     <col min="9" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="19">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="16">
       <c r="A2" s="7" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="16">
       <c r="A4" s="30" t="s">
         <v>162</v>
       </c>
@@ -5703,7 +6601,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5" s="3" t="s">
         <v>163</v>
       </c>
@@ -5736,7 +6634,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9">
       <c r="A6" s="3" t="s">
         <v>164</v>
       </c>
@@ -5762,7 +6660,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9">
       <c r="A7" s="3" t="s">
         <v>165</v>
       </c>
@@ -5792,7 +6690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9">
       <c r="A8" s="3" t="s">
         <v>166</v>
       </c>
@@ -5822,7 +6720,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="16" thickBot="1">
       <c r="A9" s="3" t="s">
         <v>167</v>
       </c>
@@ -5848,7 +6746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10" s="38" t="s">
         <v>172</v>
       </c>
@@ -5876,7 +6774,7 @@
       <c r="H10" s="38"/>
       <c r="I10" s="38"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9">
       <c r="A14" s="18" t="s">
         <v>89</v>
       </c>
@@ -5896,7 +6794,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9">
       <c r="A15" s="3" t="s">
         <v>172</v>
       </c>
@@ -5921,7 +6819,7 @@
         <v>4690807.3185967719</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9">
       <c r="A16" s="3" t="s">
         <v>174</v>
       </c>
@@ -5946,7 +6844,7 @@
         <v>8.1013348296248358E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
         <v>175</v>
       </c>
@@ -5971,7 +6869,7 @@
         <v>307529.23953664128</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
         <v>125</v>
       </c>
@@ -5996,7 +6894,7 @@
         <v>0.93190678647467051</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" s="3" t="s">
         <v>176</v>
       </c>
@@ -6021,12 +6919,12 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" s="65" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24" s="66" t="s">
         <v>179</v>
       </c>
@@ -6046,7 +6944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
         <v>163</v>
       </c>
@@ -6071,7 +6969,7 @@
         <v>400445.83996636991</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6">
       <c r="A26" s="3" t="s">
         <v>164</v>
       </c>
@@ -6096,7 +6994,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6">
       <c r="A27" s="3" t="s">
         <v>165</v>
       </c>
@@ -6121,7 +7019,7 @@
         <v>169846.15384615381</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6">
       <c r="A28" s="3" t="s">
         <v>166</v>
       </c>
@@ -6146,7 +7044,7 @@
         <v>207500</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="16" thickBot="1">
       <c r="A29" s="3" t="s">
         <v>167</v>
       </c>
@@ -6171,7 +7069,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6">
       <c r="A30" s="38" t="s">
         <v>180</v>
       </c>
@@ -6205,7 +7103,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F304AFEB-5956-4DCB-983B-70C902E234BF}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.33203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" style="3" customWidth="1"/>
@@ -6216,17 +7114,17 @@
     <col min="7" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="19">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="16">
       <c r="A2" s="20" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" s="73" t="s">
         <v>89</v>
       </c>
@@ -6246,7 +7144,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
         <v>210</v>
       </c>
@@ -6271,7 +7169,7 @@
         <v>7138560.7763938336</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
         <v>211</v>
       </c>
@@ -6296,7 +7194,7 @@
         <v>6013047.6939824056</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="16" thickBot="1">
       <c r="A7" s="3" t="s">
         <v>212</v>
       </c>
@@ -6321,7 +7219,7 @@
         <v>4430666.7218817724</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" s="74" t="s">
         <v>213</v>
       </c>
@@ -6346,7 +7244,7 @@
         <v>8720941.7484944649</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" s="71" t="s">
         <v>214</v>
       </c>
@@ -6370,7 +7268,7 @@
         <v>-69741.223845260218</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" s="18" t="s">
         <v>215</v>
       </c>
@@ -6380,7 +7278,7 @@
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
         <v>216</v>
       </c>
@@ -6405,7 +7303,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
         <v>217</v>
       </c>
@@ -6430,7 +7328,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="16" thickBot="1">
       <c r="A14" s="3" t="s">
         <v>218</v>
       </c>
@@ -6455,7 +7353,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15" s="74" t="s">
         <v>219</v>
       </c>
@@ -6488,7 +7386,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A147393-B045-4823-A500-61B421CDA990}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.33203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="21.1640625" style="3" customWidth="1"/>
@@ -6499,20 +7397,20 @@
     <col min="7" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="21">
       <c r="A1" s="119" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="119"/>
       <c r="C1" s="119"/>
     </row>
-    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="16">
       <c r="A2" s="120" t="s">
         <v>182</v>
       </c>
       <c r="B2" s="120"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" s="22"/>
       <c r="B4" s="72" t="s">
         <v>13</v>
@@ -6530,7 +7428,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" s="80" t="s">
         <v>155</v>
       </c>
@@ -6555,7 +7453,7 @@
         <v>57901659.630749986</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="16" thickBot="1">
       <c r="A6" s="3" t="s">
         <v>198</v>
       </c>
@@ -6580,7 +7478,7 @@
         <v>38504603.65444874</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" s="74" t="s">
         <v>183</v>
       </c>
@@ -6605,7 +7503,7 @@
         <v>19397055.976301245</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" s="87" t="s">
         <v>184</v>
       </c>
@@ -6630,7 +7528,7 @@
         <v>0.33500000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -6655,7 +7553,7 @@
         <v>3065660.5415499997</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -6680,7 +7578,7 @@
         <v>6683329.925999999</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="16" thickBot="1">
       <c r="A11" s="80" t="s">
         <v>187</v>
       </c>
@@ -6705,7 +7603,7 @@
         <v>9748990.4675499983</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" s="74" t="s">
         <v>188</v>
       </c>
@@ -6730,7 +7628,7 @@
         <v>9648065.5087512471</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" s="89" t="s">
         <v>189</v>
       </c>
@@ -6755,7 +7653,7 @@
         <v>0.16662847956826826</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="16" thickBot="1">
       <c r="A14" s="3" t="s">
         <v>190</v>
       </c>
@@ -6780,7 +7678,7 @@
         <v>1127791.9938125238</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15" s="74" t="s">
         <v>191</v>
       </c>
@@ -6805,7 +7703,7 @@
         <v>8520273.5149387233</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" s="89" t="s">
         <v>192</v>
       </c>
@@ -6830,7 +7728,7 @@
         <v>0.14715076509506197</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="16" thickBot="1">
       <c r="A17" s="3" t="s">
         <v>193</v>
       </c>
@@ -6850,7 +7748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" s="74" t="s">
         <v>194</v>
       </c>
@@ -6875,7 +7773,7 @@
         <v>8520273.5149387233</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="16" thickBot="1">
       <c r="A19" s="3" t="s">
         <v>195</v>
       </c>
@@ -6900,7 +7798,7 @@
         <v>2130068.3787346808</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="16">
       <c r="A20" s="84" t="s">
         <v>196</v>
       </c>
@@ -6925,7 +7823,7 @@
         <v>6390205.1362040425</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21" s="89" t="s">
         <v>197</v>
       </c>
@@ -6950,7 +7848,7 @@
         <v>0.11036307382129647</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23" s="121" t="s">
         <v>199</v>
       </c>
@@ -6960,7 +7858,7 @@
       <c r="E23" s="79"/>
       <c r="F23" s="79"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24" s="3" t="s">
         <v>200</v>
       </c>
@@ -6985,7 +7883,7 @@
         <v>4376396.1627805755</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
         <v>201</v>
       </c>
@@ -7010,7 +7908,7 @@
         <v>1135588.7668959848</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="16" thickBot="1">
       <c r="A26" s="3" t="s">
         <v>202</v>
       </c>
@@ -7035,7 +7933,7 @@
         <v>3943733.3047853564</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6">
       <c r="A27" s="74" t="s">
         <v>203</v>
       </c>
@@ -7060,7 +7958,7 @@
         <v>9455718.2344619166</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6">
       <c r="A28" s="86" t="s">
         <v>204</v>
       </c>
@@ -7098,7 +7996,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{904CB537-A7B5-44B3-BFF4-7EF29F66F82D}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.6640625" style="3" customWidth="1"/>
     <col min="2" max="2" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
@@ -7107,7 +8005,7 @@
     <col min="7" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="21">
       <c r="A1" s="122" t="s">
         <v>0</v>
       </c>
@@ -7117,12 +8015,12 @@
       <c r="E1" s="122"/>
       <c r="F1" s="122"/>
     </row>
-    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="16">
       <c r="A2" s="20" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" s="98"/>
       <c r="B4" s="72" t="s">
         <v>13</v>
@@ -7140,12 +8038,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" s="80" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
         <v>222</v>
       </c>
@@ -7170,7 +8068,7 @@
         <v>6390205.1362040425</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
         <v>223</v>
       </c>
@@ -7195,7 +8093,7 @@
         <v>1127791.9938125238</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="16" thickBot="1">
       <c r="A8" s="3" t="s">
         <v>224</v>
       </c>
@@ -7220,7 +8118,7 @@
         <v>69741.223845260218</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" s="74" t="s">
         <v>225</v>
       </c>
@@ -7245,12 +8143,12 @@
         <v>7587738.3538618265</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" s="80" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="16" thickBot="1">
       <c r="A12" s="3" t="s">
         <v>227</v>
       </c>
@@ -7275,7 +8173,7 @@
         <v>-4690807.3185967719</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" s="74" t="s">
         <v>228</v>
       </c>
@@ -7300,12 +8198,12 @@
         <v>-4690807.3185967719</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15" s="80" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="16" thickBot="1">
       <c r="A16" s="3" t="s">
         <v>230</v>
       </c>
@@ -7325,7 +8223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" s="74" t="s">
         <v>231</v>
       </c>
@@ -7350,7 +8248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" s="80" t="s">
         <v>232</v>
       </c>
@@ -7375,7 +8273,7 @@
         <v>2896931.0352650546</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="16" thickBot="1">
       <c r="A20" s="3" t="s">
         <v>233</v>
       </c>
@@ -7399,7 +8297,7 @@
         <v>15508494.500989828</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="16">
       <c r="A21" s="84" t="s">
         <v>234</v>
       </c>
@@ -7434,244 +8332,245 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AFE6724-34F6-4A41-8D1C-2005F91845F7}">
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:G13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19.83203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="3"/>
+    <col min="1" max="1" width="8.83203125" style="3"/>
+    <col min="2" max="2" width="24.5" style="3" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19.83203125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="2" spans="2:7" ht="19">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="96" t="s">
+    <row r="3" spans="2:7">
+      <c r="B3" s="96" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
+    <row r="5" spans="2:7">
+      <c r="B5" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="C5" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="72" t="s">
+      <c r="D5" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="72" t="s">
+      <c r="E5" s="72" t="s">
         <v>237</v>
       </c>
-      <c r="E4" s="72" t="s">
+      <c r="F5" s="72" t="s">
         <v>238</v>
       </c>
-      <c r="F4" s="72" t="s">
+      <c r="G5" s="72" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+    <row r="6" spans="2:7">
+      <c r="B6" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B5" s="12">
+      <c r="C6" s="12">
         <f>'P&amp;L'!C5</f>
         <v>52991955</v>
       </c>
-      <c r="C5" s="12">
+      <c r="D6" s="12">
         <f>'P&amp;L'!D5</f>
         <v>52478718.749999985</v>
       </c>
-      <c r="D5" s="12">
-        <f>C5-B5</f>
+      <c r="E6" s="12">
+        <f>D6-C6</f>
         <v>-513236.2500000149</v>
       </c>
-      <c r="E5" s="13">
-        <f>IFERROR(D5/B5,0)</f>
+      <c r="F6" s="13">
+        <f>IFERROR(E6/C6,0)</f>
         <v>-9.6851729663496068E-3</v>
       </c>
-      <c r="F5" s="25" t="str">
-        <f>IF(D5&gt;=0,"Favorable","Unfavorable")</f>
+      <c r="G6" s="25" t="str">
+        <f>IF(E6&gt;=0,"Favorable","Unfavorable")</f>
         <v>Unfavorable</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="7" spans="2:7">
+      <c r="B7" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B6" s="12">
+      <c r="C7" s="12">
         <f>'P&amp;L'!C6</f>
         <v>36034529.399999999</v>
       </c>
-      <c r="C6" s="12">
+      <c r="D7" s="12">
         <f>'P&amp;L'!D6</f>
         <v>36210315.937499985</v>
       </c>
-      <c r="D6" s="12">
-        <f t="shared" ref="D6:D12" si="0">C6-B6</f>
+      <c r="E7" s="12">
+        <f t="shared" ref="E7:E13" si="0">D7-C7</f>
         <v>175786.53749998659</v>
       </c>
-      <c r="E6" s="13">
-        <f t="shared" ref="E6:E12" si="1">IFERROR(D6/B6,0)</f>
+      <c r="F7" s="13">
+        <f t="shared" ref="F7:F13" si="1">IFERROR(E7/C7,0)</f>
         <v>4.8782803723804585E-3</v>
       </c>
-      <c r="F6" s="25" t="str">
-        <f>IF(D6&lt;=0,"Favorable","Unfavorable")</f>
+      <c r="G7" s="25" t="str">
+        <f>IF(E7&lt;=0,"Favorable","Unfavorable")</f>
         <v>Unfavorable</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+    <row r="8" spans="2:7">
+      <c r="B8" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B7" s="12">
+      <c r="C8" s="12">
         <f>'P&amp;L'!C7</f>
         <v>16957425.600000001</v>
       </c>
-      <c r="C7" s="12">
+      <c r="D8" s="12">
         <f>'P&amp;L'!D7</f>
         <v>16268402.8125</v>
       </c>
-      <c r="D7" s="12">
+      <c r="E8" s="12">
         <f t="shared" si="0"/>
         <v>-689022.78750000149</v>
       </c>
-      <c r="E7" s="13">
+      <c r="F8" s="13">
         <f t="shared" si="1"/>
         <v>-4.0632511311150997E-2</v>
       </c>
-      <c r="F7" s="25" t="str">
-        <f t="shared" ref="F7:F12" si="2">IF(D7&gt;=0,"Favorable","Unfavorable")</f>
+      <c r="G8" s="25" t="str">
+        <f t="shared" ref="G8:G13" si="2">IF(E8&gt;=0,"Favorable","Unfavorable")</f>
         <v>Unfavorable</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+    <row r="9" spans="2:7">
+      <c r="B9" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B8" s="13">
+      <c r="C9" s="13">
         <f>'P&amp;L'!C8</f>
         <v>0.32</v>
       </c>
-      <c r="C8" s="13">
+      <c r="D9" s="13">
         <f>'P&amp;L'!D8</f>
         <v>0.31000000000000011</v>
       </c>
-      <c r="D8" s="13">
+      <c r="E9" s="13">
         <f t="shared" si="0"/>
         <v>-9.9999999999998979E-3</v>
       </c>
-      <c r="E8" s="13">
+      <c r="F9" s="13">
         <f t="shared" si="1"/>
         <v>-3.1249999999999681E-2</v>
       </c>
-      <c r="F8" s="25" t="str">
+      <c r="G9" s="25" t="str">
         <f t="shared" si="2"/>
         <v>Unfavorable</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+    <row r="10" spans="2:7">
+      <c r="B10" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B9" s="12">
+      <c r="C10" s="12">
         <f>'P&amp;L'!C11</f>
         <v>8174967</v>
       </c>
-      <c r="C9" s="12">
+      <c r="D10" s="12">
         <f>'P&amp;L'!D11</f>
         <v>8238488.75</v>
       </c>
-      <c r="D9" s="12">
+      <c r="E10" s="12">
         <f t="shared" si="0"/>
         <v>63521.75</v>
       </c>
-      <c r="E9" s="13">
+      <c r="F10" s="13">
         <f t="shared" si="1"/>
         <v>7.7702760145698449E-3</v>
       </c>
-      <c r="F9" s="25" t="str">
-        <f>IF(D9&lt;=0,"Favorable","Unfavorable")</f>
+      <c r="G10" s="25" t="str">
+        <f>IF(E10&lt;=0,"Favorable","Unfavorable")</f>
         <v>Unfavorable</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+    <row r="11" spans="2:7">
+      <c r="B11" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B10" s="12">
+      <c r="C11" s="12">
         <f>'P&amp;L'!C12</f>
         <v>8782458.6000000015</v>
       </c>
-      <c r="C10" s="12">
+      <c r="D11" s="12">
         <f>'P&amp;L'!D12</f>
         <v>8029914.0625</v>
       </c>
-      <c r="D10" s="12">
+      <c r="E11" s="12">
         <f t="shared" si="0"/>
         <v>-752544.53750000149</v>
       </c>
-      <c r="E10" s="13">
+      <c r="F11" s="13">
         <f t="shared" si="1"/>
         <v>-8.5687228574012453E-2</v>
       </c>
-      <c r="F10" s="25" t="str">
+      <c r="G11" s="25" t="str">
         <f t="shared" si="2"/>
         <v>Unfavorable</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+    <row r="12" spans="2:7">
+      <c r="B12" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B11" s="12">
+      <c r="C12" s="12">
         <f>'P&amp;L'!C15</f>
         <v>8374020.2461748645</v>
       </c>
-      <c r="C11" s="12">
+      <c r="D12" s="12">
         <f>'P&amp;L'!D15</f>
         <v>7619344.7292151097</v>
       </c>
-      <c r="D11" s="12">
+      <c r="E12" s="12">
         <f t="shared" si="0"/>
         <v>-754675.51695975475</v>
       </c>
-      <c r="E11" s="13">
+      <c r="F12" s="13">
         <f t="shared" si="1"/>
         <v>-9.0121052346927397E-2</v>
       </c>
-      <c r="F11" s="25" t="str">
+      <c r="G12" s="25" t="str">
         <f t="shared" si="2"/>
         <v>Unfavorable</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+    <row r="13" spans="2:7">
+      <c r="B13" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B12" s="12">
+      <c r="C13" s="12">
         <f>'P&amp;L'!C20</f>
         <v>6280515.1846311484</v>
       </c>
-      <c r="C12" s="12">
+      <c r="D13" s="12">
         <f>'P&amp;L'!D20</f>
         <v>5714508.5469113328</v>
       </c>
-      <c r="D12" s="12">
+      <c r="E13" s="12">
         <f t="shared" si="0"/>
         <v>-566006.6377198156</v>
       </c>
-      <c r="E12" s="13">
+      <c r="F13" s="13">
         <f t="shared" si="1"/>
         <v>-9.0121052346927313E-2</v>
       </c>
-      <c r="F12" s="25" t="str">
+      <c r="G13" s="25" t="str">
         <f t="shared" si="2"/>
         <v>Unfavorable</v>
       </c>
@@ -7684,7 +8583,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0DA7B3E-B2AE-4D49-8E45-6809B3A9C6C3}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.33203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="20" style="3" customWidth="1"/>
@@ -7694,17 +8593,17 @@
     <col min="6" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="19">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" s="95" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" s="102" t="s">
         <v>89</v>
       </c>
@@ -7721,7 +8620,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
         <v>155</v>
       </c>
@@ -7742,7 +8641,7 @@
         <v>57901659.630749986</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" s="71" t="s">
         <v>241</v>
       </c>
@@ -7762,7 +8661,7 @@
         <v>2.4999999999999689E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
         <v>184</v>
       </c>
@@ -7783,7 +8682,7 @@
         <v>0.33500000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
         <v>189</v>
       </c>
@@ -7804,7 +8703,7 @@
         <v>0.16624187959081937</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
         <v>192</v>
       </c>
@@ -7825,7 +8724,7 @@
         <v>0.14715076509506197</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
         <v>197</v>
       </c>
@@ -7846,7 +8745,7 @@
         <v>0.11036307382129647</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" s="80" t="s">
         <v>196</v>
       </c>
@@ -7867,7 +8766,7 @@
         <v>6390205.1362040425</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12" s="80" t="s">
         <v>242</v>
       </c>
@@ -7888,7 +8787,7 @@
         <v>2896931.0352650546</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
         <v>234</v>
       </c>
@@ -7917,7 +8816,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A96C0DD6-464B-0749-96EE-2AC06823DAFA}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="18" bestFit="1" customWidth="1"/>
@@ -7925,7 +8824,7 @@
     <col min="5" max="6" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" s="113" t="s">
         <v>324</v>
       </c>
@@ -7945,7 +8844,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" s="114" t="s">
         <v>50</v>
       </c>
@@ -7965,7 +8864,7 @@
         <v>12577237.377249997</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" s="114" t="s">
         <v>49</v>
       </c>
@@ -7985,7 +8884,7 @@
         <v>19590351.306499999</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" s="114" t="s">
         <v>48</v>
       </c>
@@ -8005,7 +8904,7 @@
         <v>25734070.946999993</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" s="114" t="s">
         <v>325</v>
       </c>
@@ -8033,192 +8932,193 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F5058BB-20BB-4936-9D4A-179D8AA2FD3F}">
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:I12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5" style="3" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14" style="3" customWidth="1"/>
-    <col min="7" max="8" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.83203125" style="3"/>
+    <col min="1" max="1" width="8.83203125" style="3"/>
+    <col min="2" max="2" width="33.5" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" style="3" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14" style="3" customWidth="1"/>
+    <col min="8" max="9" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+    <row r="2" spans="2:9" ht="24">
+      <c r="B2" s="78" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="96" t="s">
+    <row r="3" spans="2:9">
+      <c r="B3" s="96" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="102" t="s">
+    <row r="5" spans="2:9">
+      <c r="B5" s="102" t="s">
         <v>245</v>
       </c>
-      <c r="B4" s="103" t="s">
+      <c r="C5" s="103" t="s">
         <v>246</v>
       </c>
-      <c r="C4" s="103" t="s">
+      <c r="D5" s="103" t="s">
         <v>247</v>
       </c>
-      <c r="D4" s="103" t="s">
+      <c r="E5" s="103" t="s">
         <v>155</v>
       </c>
-      <c r="E4" s="103" t="s">
+      <c r="F5" s="103" t="s">
         <v>183</v>
       </c>
-      <c r="F4" s="103" t="s">
+      <c r="G5" s="103" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="103" t="s">
+      <c r="H5" s="103" t="s">
         <v>248</v>
       </c>
-      <c r="H4" s="103" t="s">
+      <c r="I5" s="103" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+    <row r="6" spans="2:9">
+      <c r="B6" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B5" s="16">
+      <c r="C6" s="16">
         <v>-0.03</v>
       </c>
-      <c r="C5" s="16">
+      <c r="D6" s="16">
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="D5" s="10">
-        <f>'P&amp;L'!$B$5*(1+Assumptions!$E$5+Scenario_Analysis!B5)</f>
+      <c r="E6" s="10">
+        <f>'P&amp;L'!$B$5*(1+Assumptions!$E$5+Scenario_Analysis!C6)</f>
         <v>50949000</v>
       </c>
-      <c r="E5" s="10">
-        <f>D5*F5</f>
+      <c r="F6" s="10">
+        <f>E6*G6</f>
         <v>15029955</v>
       </c>
-      <c r="F5" s="16">
-        <f>Assumptions!$E$8+Scenario_Analysis!C5</f>
+      <c r="G6" s="16">
+        <f>Assumptions!$E$8+Scenario_Analysis!D6</f>
         <v>0.29499999999999998</v>
       </c>
-      <c r="G5" s="10">
-        <f>E5-'P&amp;L'!$D$11-'P&amp;L'!$D$14</f>
+      <c r="H6" s="10">
+        <f>F6-'P&amp;L'!$D$11-'P&amp;L'!$D$14</f>
         <v>6380896.9167151097</v>
       </c>
-      <c r="H5" s="10">
-        <f>G5*(1-Assumptions!$E$16)</f>
+      <c r="I6" s="10">
+        <f>H6*(1-Assumptions!$E$16)</f>
         <v>4785672.6875363328</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="7" spans="2:9">
+      <c r="B7" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B6" s="16">
+      <c r="C7" s="16">
         <v>0</v>
       </c>
-      <c r="C6" s="16">
+      <c r="D7" s="16">
         <v>0</v>
       </c>
-      <c r="D6" s="10">
-        <f>'P&amp;L'!$B$5*(1+Assumptions!$E$5+Scenario_Analysis!B6)</f>
+      <c r="E7" s="10">
+        <f>'P&amp;L'!$B$5*(1+Assumptions!$E$5+Scenario_Analysis!C7)</f>
         <v>52447500</v>
       </c>
-      <c r="E6" s="10">
-        <f t="shared" ref="E6:E7" si="0">D6*F6</f>
+      <c r="F7" s="10">
+        <f t="shared" ref="F7:F8" si="0">E7*G7</f>
         <v>16258725</v>
       </c>
-      <c r="F6" s="16">
-        <f>Assumptions!$E$8+Scenario_Analysis!C6</f>
+      <c r="G7" s="16">
+        <f>Assumptions!$E$8+Scenario_Analysis!D7</f>
         <v>0.31</v>
       </c>
-      <c r="G6" s="10">
-        <f>E6-'P&amp;L'!$D$11-'P&amp;L'!$D$14</f>
+      <c r="H7" s="10">
+        <f>F7-'P&amp;L'!$D$11-'P&amp;L'!$D$14</f>
         <v>7609666.9167151097</v>
       </c>
-      <c r="H6" s="10">
-        <f>G6*(1-Assumptions!$E$16)</f>
+      <c r="I7" s="10">
+        <f>H7*(1-Assumptions!$E$16)</f>
         <v>5707250.1875363328</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+    <row r="8" spans="2:9">
+      <c r="B8" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="16">
+      <c r="C8" s="16">
         <v>0.02</v>
       </c>
-      <c r="C7" s="11">
+      <c r="D8" s="11">
         <v>0.01</v>
       </c>
-      <c r="D7" s="10">
-        <f>'P&amp;L'!$B$5*(1+Assumptions!$E$5+Scenario_Analysis!B7)</f>
+      <c r="E8" s="10">
+        <f>'P&amp;L'!$B$5*(1+Assumptions!$E$5+Scenario_Analysis!C8)</f>
         <v>53446500</v>
       </c>
-      <c r="E7" s="10">
+      <c r="F8" s="10">
         <f t="shared" si="0"/>
         <v>17102880</v>
       </c>
-      <c r="F7" s="16">
-        <f>Assumptions!$E$8+Scenario_Analysis!C7</f>
+      <c r="G8" s="16">
+        <f>Assumptions!$E$8+Scenario_Analysis!D8</f>
         <v>0.32</v>
       </c>
-      <c r="G7" s="10">
-        <f>E7-'P&amp;L'!$D$11-'P&amp;L'!$D$14</f>
+      <c r="H8" s="10">
+        <f>F8-'P&amp;L'!$D$11-'P&amp;L'!$D$14</f>
         <v>8453821.9167151097</v>
       </c>
-      <c r="H7" s="10">
-        <f>G7*(1-Assumptions!$E$16)</f>
+      <c r="I8" s="10">
+        <f>H8*(1-Assumptions!$E$16)</f>
         <v>6340366.4375363328</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="27" t="s">
+    <row r="10" spans="2:9">
+      <c r="B10" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="B9" s="27" t="str">
+      <c r="C10" s="27" t="str">
         <f>'Control Panel'!C4</f>
         <v>Upside</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="97" t="s">
+    <row r="11" spans="2:9">
+      <c r="C11" s="97" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="97" t="s">
+      <c r="D11" s="97" t="s">
         <v>183</v>
       </c>
-      <c r="D10" s="97" t="s">
+      <c r="E11" s="97" t="s">
         <v>184</v>
       </c>
-      <c r="E10" s="97" t="s">
+      <c r="F11" s="97" t="s">
         <v>248</v>
       </c>
-      <c r="F10" s="97" t="s">
+      <c r="G11" s="97" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="104">
-        <f>INDEX(D5:D7,MATCH($B$9,$A$5:$A$7,0))</f>
+    <row r="12" spans="2:9">
+      <c r="C12" s="104">
+        <f>INDEX(E6:E8,MATCH($C$10,$B$6:$B$8,0))</f>
         <v>53446500</v>
       </c>
-      <c r="C11" s="104">
-        <f t="shared" ref="C11:F11" si="1">INDEX(E5:E7,MATCH($B$9,$A$5:$A$7,0))</f>
+      <c r="D12" s="104">
+        <f t="shared" ref="D12:G12" si="1">INDEX(F6:F8,MATCH($C$10,$B$6:$B$8,0))</f>
         <v>17102880</v>
       </c>
-      <c r="D11" s="105">
+      <c r="E12" s="105">
         <f t="shared" si="1"/>
         <v>0.32</v>
       </c>
-      <c r="E11" s="104">
+      <c r="F12" s="104">
         <f t="shared" si="1"/>
         <v>8453821.9167151097</v>
       </c>
-      <c r="F11" s="104">
+      <c r="G12" s="104">
         <f t="shared" si="1"/>
         <v>6340366.4375363328</v>
       </c>
@@ -8231,7 +9131,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DEC588F-0AA4-452F-8C2D-960F554B99FB}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="3" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" style="3" customWidth="1"/>
@@ -8241,17 +9141,17 @@
     <col min="6" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="19">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" s="96" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" s="102" t="s">
         <v>35</v>
       </c>
@@ -8268,10 +9168,9 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="str">
-        <f>[1]Revenue_Model!A3</f>
-        <v>Precision Components</v>
+    <row r="5" spans="1:6">
+      <c r="A5" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="B5" s="15">
         <f>Revenue_Model!H5</f>
@@ -8291,10 +9190,9 @@
       </c>
       <c r="F5" s="15"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="str">
-        <f>[1]Revenue_Model!A4</f>
-        <v>Industrial Assemblies</v>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="B6" s="15">
         <f>Revenue_Model!H6</f>
@@ -8314,10 +9212,9 @@
       </c>
       <c r="F6" s="15"/>
     </row>
-    <row r="7" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="str">
-        <f>[1]Revenue_Model!A5</f>
-        <v>Automotive Components</v>
+    <row r="7" spans="1:6" ht="16" thickBot="1">
+      <c r="A7" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="B7" s="15">
         <f>Revenue_Model!H7</f>
@@ -8337,7 +9234,7 @@
       </c>
       <c r="F7" s="15"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" s="74" t="s">
         <v>256</v>
       </c>
@@ -8359,7 +9256,7 @@
       </c>
       <c r="F8" s="15"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" s="108" t="s">
         <v>257</v>
       </c>
@@ -8387,7 +9284,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14E4ACB-4A46-41B4-ACDC-172F9291B6F3}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.83203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="16.1640625" style="3" customWidth="1"/>
@@ -8398,23 +9295,23 @@
     <col min="7" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="21">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="19">
       <c r="A2" s="109" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" s="27" t="str">
         <f>CONCATENATE("Scenario: ",'Control Panel'!C4,"| Model Version: ",'Control Panel'!C11)</f>
         <v>Scenario: Upside| Model Version: v1.0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" s="18" t="s">
         <v>262</v>
       </c>
@@ -8434,7 +9331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
         <v>263</v>
       </c>
@@ -8459,7 +9356,7 @@
         <v>57901659.630749986</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -8484,7 +9381,7 @@
         <v>0.33500000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
         <v>189</v>
       </c>
@@ -8509,7 +9406,7 @@
         <v>0.16662847956826826</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
         <v>197</v>
       </c>
@@ -8534,7 +9431,7 @@
         <v>0.11036307382129647</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
         <v>264</v>
       </c>
@@ -8559,7 +9456,7 @@
         <v>6390205.1362040425</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
         <v>265</v>
       </c>
@@ -8584,32 +9481,32 @@
         <v>8.1013348296248358E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="53">
         <f>CapEx!B18</f>
         <v>0.90476190476190477</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="53">
         <f>CapEx!C18</f>
         <v>0.89884821933295644</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="53">
         <f>CapEx!D18</f>
         <v>0.94591316716250529</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="53">
         <f>CapEx!E18</f>
         <v>0.94194674684257818</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="53">
         <f>CapEx!F18</f>
         <v>0.93190678647467051</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
         <v>219</v>
       </c>
@@ -8634,7 +9531,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
         <v>266</v>
       </c>
@@ -8659,7 +9556,7 @@
         <v>0.90305171652321925</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
         <v>267</v>
       </c>
@@ -8690,9 +9587,461 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CFC0599-D08A-DE4A-A545-635EC13E28B9}">
+  <dimension ref="D2:P42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="8.83203125" style="3"/>
+    <col min="3" max="3" width="3" style="3" customWidth="1"/>
+    <col min="4" max="4" width="23" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="17.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="12" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" style="3" customWidth="1"/>
+    <col min="12" max="16" width="12" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="8.83203125" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="4:16" ht="30.75" customHeight="1"/>
+    <row r="3" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D3" s="124" t="s">
+        <v>331</v>
+      </c>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="124"/>
+      <c r="K3" s="124"/>
+      <c r="L3" s="124"/>
+      <c r="M3" s="124"/>
+      <c r="N3" s="124"/>
+      <c r="O3" s="124"/>
+      <c r="P3" s="124"/>
+    </row>
+    <row r="4" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D4" s="124"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="124"/>
+      <c r="N4" s="124"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+    </row>
+    <row r="5" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D5" s="125" t="s">
+        <v>332</v>
+      </c>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="125"/>
+      <c r="O5" s="125"/>
+      <c r="P5" s="125"/>
+    </row>
+    <row r="6" spans="4:16" ht="36" customHeight="1">
+      <c r="D6" s="126" t="str">
+        <f>Management_Dashboard!A4</f>
+        <v>Scenario: Upside| Model Version: v1.0</v>
+      </c>
+      <c r="E6" s="126"/>
+      <c r="F6" s="126"/>
+      <c r="G6" s="126"/>
+      <c r="H6" s="127"/>
+      <c r="I6" s="127"/>
+      <c r="J6" s="127"/>
+      <c r="K6" s="127"/>
+      <c r="L6" s="127"/>
+      <c r="M6" s="127"/>
+      <c r="N6" s="127"/>
+      <c r="O6" s="127"/>
+      <c r="P6" s="127"/>
+    </row>
+    <row r="7" spans="4:16" ht="30.75" customHeight="1">
+      <c r="E7" s="128" t="s">
+        <v>333</v>
+      </c>
+      <c r="F7" s="128"/>
+      <c r="H7" s="128" t="s">
+        <v>334</v>
+      </c>
+      <c r="I7" s="128"/>
+      <c r="K7" s="128" t="s">
+        <v>335</v>
+      </c>
+      <c r="L7" s="128"/>
+    </row>
+    <row r="8" spans="4:16" ht="30.75" customHeight="1">
+      <c r="E8" s="129">
+        <f>Management_Dashboard!D7</f>
+        <v>52478718.749999985</v>
+      </c>
+      <c r="F8" s="129"/>
+      <c r="H8" s="130">
+        <f>Management_Dashboard!D8</f>
+        <v>0.31000000000000011</v>
+      </c>
+      <c r="I8" s="130"/>
+      <c r="K8" s="130">
+        <f>Management_Dashboard!D9</f>
+        <v>0.15301276886642745</v>
+      </c>
+      <c r="L8" s="130"/>
+    </row>
+    <row r="9" spans="4:16" ht="30.75" customHeight="1"/>
+    <row r="10" spans="4:16" ht="30.75" customHeight="1">
+      <c r="E10" s="128" t="s">
+        <v>336</v>
+      </c>
+      <c r="F10" s="128"/>
+      <c r="H10" s="128" t="s">
+        <v>337</v>
+      </c>
+      <c r="I10" s="128"/>
+      <c r="K10" s="128" t="s">
+        <v>338</v>
+      </c>
+      <c r="L10" s="128"/>
+    </row>
+    <row r="11" spans="4:16" ht="30.75" customHeight="1">
+      <c r="E11" s="131">
+        <f>Management_Dashboard!D11</f>
+        <v>5714508.5469113328</v>
+      </c>
+      <c r="F11" s="131"/>
+      <c r="H11" s="131">
+        <f>Management_Dashboard!D16</f>
+        <v>10087908.97042425</v>
+      </c>
+      <c r="I11" s="131"/>
+      <c r="K11" s="130">
+        <f>Management_Dashboard!D13</f>
+        <v>0.94591316716250529</v>
+      </c>
+      <c r="L11" s="130"/>
+    </row>
+    <row r="12" spans="4:16" ht="30.75" customHeight="1"/>
+    <row r="13" spans="4:16" ht="36" customHeight="1">
+      <c r="D13" s="132" t="s">
+        <v>339</v>
+      </c>
+      <c r="E13" s="133"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="133"/>
+      <c r="H13" s="133"/>
+      <c r="I13" s="133"/>
+      <c r="J13" s="133"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="133"/>
+      <c r="M13" s="133"/>
+      <c r="N13" s="133"/>
+      <c r="O13" s="133"/>
+      <c r="P13" s="133"/>
+    </row>
+    <row r="14" spans="4:16" ht="30.75" customHeight="1"/>
+    <row r="15" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D15" s="134" t="s">
+        <v>340</v>
+      </c>
+      <c r="E15" s="135" t="s">
+        <v>341</v>
+      </c>
+      <c r="F15" s="135"/>
+    </row>
+    <row r="16" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D16" s="136" t="s">
+        <v>342</v>
+      </c>
+      <c r="E16" s="137">
+        <f>Management_Dashboard!B7/1000000</f>
+        <v>49.95</v>
+      </c>
+      <c r="F16" s="137"/>
+    </row>
+    <row r="17" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D17" s="136" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="137">
+        <f>Management_Dashboard!C7/1000000</f>
+        <v>52.991954999999997</v>
+      </c>
+      <c r="F17" s="137"/>
+    </row>
+    <row r="18" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D18" s="136" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="137">
+        <f>Management_Dashboard!D7/1000000</f>
+        <v>52.478718749999985</v>
+      </c>
+      <c r="F18" s="137"/>
+    </row>
+    <row r="19" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D19" s="136" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="137">
+        <f>Management_Dashboard!E7/1000000</f>
+        <v>56.489424030000002</v>
+      </c>
+      <c r="F19" s="137"/>
+    </row>
+    <row r="20" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D20" s="136" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="137">
+        <f>Management_Dashboard!F7/1000000</f>
+        <v>57.901659630749982</v>
+      </c>
+      <c r="F20" s="137"/>
+    </row>
+    <row r="21" spans="4:16" ht="30.75" customHeight="1"/>
+    <row r="22" spans="4:16" ht="30.75" customHeight="1"/>
+    <row r="23" spans="4:16" ht="30.75" customHeight="1"/>
+    <row r="24" spans="4:16" ht="30.75" customHeight="1"/>
+    <row r="25" spans="4:16" ht="30.75" customHeight="1"/>
+    <row r="26" spans="4:16" ht="30.75" customHeight="1"/>
+    <row r="27" spans="4:16" ht="30.75" customHeight="1"/>
+    <row r="28" spans="4:16" ht="36" customHeight="1">
+      <c r="D28" s="132" t="s">
+        <v>343</v>
+      </c>
+      <c r="E28" s="133"/>
+      <c r="F28" s="133"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="133"/>
+      <c r="I28" s="133"/>
+      <c r="J28" s="133"/>
+      <c r="K28" s="133"/>
+      <c r="L28" s="133"/>
+      <c r="M28" s="133"/>
+      <c r="N28" s="133"/>
+      <c r="O28" s="133"/>
+      <c r="P28" s="133"/>
+    </row>
+    <row r="29" spans="4:16" ht="30.75" customHeight="1"/>
+    <row r="30" spans="4:16" ht="36" customHeight="1">
+      <c r="D30" s="138" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="138" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="138" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="138" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="31" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D31" s="139" t="s">
+        <v>341</v>
+      </c>
+      <c r="E31" s="140">
+        <f>Management_Dashboard!C7/1000000</f>
+        <v>52.991954999999997</v>
+      </c>
+      <c r="F31" s="140">
+        <f>Management_Dashboard!D7/1000000</f>
+        <v>52.478718749999985</v>
+      </c>
+      <c r="G31" s="141">
+        <f t="shared" ref="G31:G36" si="0">F31-E31</f>
+        <v>-0.51323625000001272</v>
+      </c>
+    </row>
+    <row r="32" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D32" s="139" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="142">
+        <f>Management_Dashboard!C8</f>
+        <v>0.32</v>
+      </c>
+      <c r="F32" s="146">
+        <f>Management_Dashboard!D8</f>
+        <v>0.31000000000000011</v>
+      </c>
+      <c r="G32" s="143">
+        <f t="shared" si="0"/>
+        <v>-9.9999999999998979E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D33" s="139" t="s">
+        <v>345</v>
+      </c>
+      <c r="E33" s="142">
+        <f>Management_Dashboard!C9</f>
+        <v>0.16573192289282404</v>
+      </c>
+      <c r="F33" s="146">
+        <f>Management_Dashboard!D9</f>
+        <v>0.15301276886642745</v>
+      </c>
+      <c r="G33" s="143">
+        <f t="shared" si="0"/>
+        <v>-1.271915402639659E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D34" s="139" t="s">
+        <v>346</v>
+      </c>
+      <c r="E34" s="140">
+        <f>Management_Dashboard!C11/1000000</f>
+        <v>6.280515184631148</v>
+      </c>
+      <c r="F34" s="140">
+        <f>Management_Dashboard!D11/1000000</f>
+        <v>5.7145085469113326</v>
+      </c>
+      <c r="G34" s="141">
+        <f t="shared" si="0"/>
+        <v>-0.56600663771981541</v>
+      </c>
+      <c r="L34" s="127"/>
+    </row>
+    <row r="35" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D35" s="139" t="s">
+        <v>347</v>
+      </c>
+      <c r="E35" s="140">
+        <f>Management_Dashboard!C16/1000000</f>
+        <v>11.213957187967479</v>
+      </c>
+      <c r="F35" s="140">
+        <f>Management_Dashboard!D16/1000000</f>
+        <v>10.08790897042425</v>
+      </c>
+      <c r="G35" s="141">
+        <f t="shared" si="0"/>
+        <v>-1.1260482175432287</v>
+      </c>
+      <c r="L35" s="127"/>
+    </row>
+    <row r="36" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D36" s="139" t="s">
+        <v>125</v>
+      </c>
+      <c r="E36" s="142">
+        <f>Management_Dashboard!C13</f>
+        <v>0.89884821933295644</v>
+      </c>
+      <c r="F36" s="142">
+        <f>Management_Dashboard!D13</f>
+        <v>0.94591316716250529</v>
+      </c>
+      <c r="G36" s="143">
+        <f t="shared" si="0"/>
+        <v>4.7064947829548842E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="4:16" ht="30.75" customHeight="1"/>
+    <row r="38" spans="4:16" ht="36" customHeight="1">
+      <c r="D38" s="144" t="s">
+        <v>348</v>
+      </c>
+      <c r="E38" s="133"/>
+      <c r="F38" s="133"/>
+      <c r="G38" s="133"/>
+      <c r="H38" s="133"/>
+      <c r="I38" s="133"/>
+      <c r="J38" s="133"/>
+      <c r="K38" s="133"/>
+      <c r="L38" s="133"/>
+      <c r="M38" s="133"/>
+      <c r="N38" s="133"/>
+      <c r="O38" s="133"/>
+      <c r="P38" s="133"/>
+    </row>
+    <row r="39" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D39" s="145" t="s">
+        <v>349</v>
+      </c>
+      <c r="E39" s="127"/>
+      <c r="F39" s="127"/>
+      <c r="G39" s="127"/>
+      <c r="H39" s="127"/>
+      <c r="I39" s="127"/>
+      <c r="J39" s="127"/>
+      <c r="K39" s="127"/>
+      <c r="M39" s="127"/>
+      <c r="N39" s="127"/>
+      <c r="O39" s="127"/>
+      <c r="P39" s="127"/>
+    </row>
+    <row r="40" spans="4:16" ht="30.75" customHeight="1">
+      <c r="D40" s="145" t="s">
+        <v>350</v>
+      </c>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="127"/>
+      <c r="H40" s="127"/>
+      <c r="I40" s="127"/>
+      <c r="J40" s="127"/>
+      <c r="K40" s="127"/>
+      <c r="M40" s="127"/>
+      <c r="N40" s="127"/>
+      <c r="O40" s="127"/>
+      <c r="P40" s="127"/>
+    </row>
+    <row r="41" spans="4:16" ht="30.75" customHeight="1"/>
+    <row r="42" spans="4:16" ht="30.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="D3:P4"/>
+    <mergeCell ref="D5:P5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="K7:L7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C922350E-900C-4827-84D0-17B0E243CF0A}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.5" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -8701,17 +10050,17 @@
     <col min="8" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="21">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="110" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="102" t="s">
         <v>268</v>
       </c>
@@ -8734,7 +10083,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="3" t="s">
         <v>269</v>
       </c>
@@ -8763,7 +10112,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="3" t="s">
         <v>270</v>
       </c>
@@ -8792,7 +10141,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="3" t="s">
         <v>271</v>
       </c>
@@ -8821,7 +10170,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="3" t="s">
         <v>272</v>
       </c>
@@ -8850,7 +10199,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="3" t="s">
         <v>273</v>
       </c>
@@ -8879,7 +10228,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="3" t="s">
         <v>274</v>
       </c>
@@ -8892,7 +10241,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="71" t="s">
         <v>275</v>
       </c>
@@ -8920,7 +10269,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="15" customHeight="1">
       <c r="A13" s="123" t="s">
         <v>279</v>
       </c>
@@ -8931,7 +10280,7 @@
       <c r="F13" s="123"/>
       <c r="G13" s="123"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="123"/>
       <c r="B14" s="123"/>
       <c r="C14" s="123"/>
@@ -8951,24 +10300,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49EBD83A-291D-488F-A4B3-56FE200DE784}">
   <dimension ref="B1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="3"/>
     <col min="2" max="2" width="34.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:3" ht="19">
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:3" ht="16">
       <c r="B2" s="76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:3" ht="16">
       <c r="B4" s="75" t="s">
         <v>2</v>
       </c>
@@ -8976,7 +10325,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:3">
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
@@ -8984,7 +10333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:3">
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
@@ -8992,7 +10341,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:3">
       <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
@@ -9000,7 +10349,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:3">
       <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
@@ -9008,7 +10357,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:3">
       <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
@@ -9016,7 +10365,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:3">
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
@@ -9024,7 +10373,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:3">
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
@@ -9045,7 +10394,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35844B2D-7EB9-4D56-9566-DF6D3DAE13E4}">
   <dimension ref="B1:C22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="3"/>
     <col min="2" max="2" width="21.5" style="3" customWidth="1"/>
@@ -9053,23 +10402,23 @@
     <col min="4" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:3" ht="24">
       <c r="B1" s="78" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:3" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" ht="19">
       <c r="B2" s="77" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:3">
       <c r="B4" s="18" t="s">
         <v>311</v>
       </c>
       <c r="C4" s="19"/>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:3">
       <c r="B5" s="3" t="s">
         <v>155</v>
       </c>
@@ -9078,7 +10427,7 @@
         <v>49950000</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:3">
       <c r="B6" s="3" t="s">
         <v>236</v>
       </c>
@@ -9087,7 +10436,7 @@
         <v>34465500</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:3">
       <c r="B7" s="3" t="s">
         <v>183</v>
       </c>
@@ -9096,7 +10445,7 @@
         <v>15484500</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:3">
       <c r="B8" s="3" t="s">
         <v>184</v>
       </c>
@@ -9105,7 +10454,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:3">
       <c r="B9" s="3" t="s">
         <v>187</v>
       </c>
@@ -9114,7 +10463,7 @@
         <v>7378000</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:3">
       <c r="B10" s="3" t="s">
         <v>188</v>
       </c>
@@ -9123,7 +10472,7 @@
         <v>8106500</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:3">
       <c r="B11" s="3" t="s">
         <v>189</v>
       </c>
@@ -9132,7 +10481,7 @@
         <v>0.16229229229229231</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:3">
       <c r="B12" s="3" t="s">
         <v>248</v>
       </c>
@@ -9141,7 +10490,7 @@
         <v>7906500</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:3">
       <c r="B13" s="3" t="s">
         <v>196</v>
       </c>
@@ -9150,7 +10499,7 @@
         <v>5929875</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:3">
       <c r="B14" s="3" t="s">
         <v>197</v>
       </c>
@@ -9159,13 +10508,13 @@
         <v>0.11871621621621621</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:3">
       <c r="B16" s="21" t="s">
         <v>312</v>
       </c>
       <c r="C16" s="22"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:3">
       <c r="B17" s="3" t="s">
         <v>313</v>
       </c>
@@ -9174,7 +10523,7 @@
         <v>247000</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:3">
       <c r="B18" s="3" t="s">
         <v>314</v>
       </c>
@@ -9183,7 +10532,7 @@
         <v>253333.33333333334</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:3">
       <c r="B19" s="3" t="s">
         <v>315</v>
       </c>
@@ -9192,7 +10541,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:3">
       <c r="B20" s="3" t="s">
         <v>172</v>
       </c>
@@ -9201,7 +10550,7 @@
         <v>1750000</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:3">
       <c r="B21" s="3" t="s">
         <v>265</v>
       </c>
@@ -9210,7 +10559,7 @@
         <v>3.5035035035035036E-2</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:3">
       <c r="B22" s="3" t="s">
         <v>125</v>
       </c>
@@ -9227,7 +10576,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115883F3-6621-49EC-8B5A-0157E0CE779E}">
   <dimension ref="B1:I16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="3"/>
     <col min="2" max="2" width="14.5" style="3" bestFit="1" customWidth="1"/>
@@ -9239,17 +10588,17 @@
     <col min="9" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:9" ht="19">
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:9" ht="16">
       <c r="B2" s="7" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:9" ht="16">
       <c r="B4" s="30" t="s">
         <v>12</v>
       </c>
@@ -9271,7 +10620,7 @@
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:9">
       <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
@@ -9291,7 +10640,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:9">
       <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
@@ -9311,7 +10660,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:9">
       <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
@@ -9331,7 +10680,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:9">
       <c r="B8" s="3" t="s">
         <v>30</v>
       </c>
@@ -9351,7 +10700,7 @@
         <v>0.33500000000000002</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:9">
       <c r="B9" s="3" t="s">
         <v>31</v>
       </c>
@@ -9371,7 +10720,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:9">
       <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
@@ -9391,7 +10740,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:9">
       <c r="B11" s="3" t="s">
         <v>23</v>
       </c>
@@ -9411,7 +10760,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:9">
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
@@ -9431,7 +10780,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:9">
       <c r="B13" s="3" t="s">
         <v>25</v>
       </c>
@@ -9451,7 +10800,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:9">
       <c r="B14" s="3" t="s">
         <v>26</v>
       </c>
@@ -9471,7 +10820,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:9">
       <c r="B15" s="3" t="s">
         <v>27</v>
       </c>
@@ -9491,7 +10840,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:9">
       <c r="B16" s="3" t="s">
         <v>28</v>
       </c>
@@ -9519,7 +10868,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35AF9FDB-42D1-436D-AD1B-74FB972FB2B4}">
   <dimension ref="C1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="8.83203125" style="3"/>
     <col min="3" max="3" width="15.5" style="3" customWidth="1"/>
@@ -9529,17 +10878,17 @@
     <col min="7" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:8" ht="19">
       <c r="C1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="3:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="3:8" ht="16">
       <c r="C2" s="7" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:8">
       <c r="C4" s="26" t="s">
         <v>32</v>
       </c>
@@ -9559,7 +10908,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:8">
       <c r="C5" s="27" t="s">
         <v>33</v>
       </c>
@@ -9579,7 +10928,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="3:8">
       <c r="C6" s="27" t="s">
         <v>34</v>
       </c>
@@ -9607,7 +10956,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3F15406-1EFB-47C5-9431-8AD3039A0625}">
   <dimension ref="B1:Q8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="3"/>
     <col min="2" max="2" width="21" style="3" bestFit="1" customWidth="1"/>
@@ -9629,17 +10978,17 @@
     <col min="18" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:17" ht="19">
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:17">
       <c r="B2" s="31" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:17">
       <c r="B4" s="18" t="s">
         <v>35</v>
       </c>
@@ -9689,7 +11038,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:17">
       <c r="B5" s="3" t="s">
         <v>48</v>
       </c>
@@ -9752,7 +11101,7 @@
         <v>25734070.946999993</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:17">
       <c r="B6" s="3" t="s">
         <v>49</v>
       </c>
@@ -9815,7 +11164,7 @@
         <v>19590351.306499999</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" ht="16" thickBot="1">
       <c r="B7" s="3" t="s">
         <v>50</v>
       </c>
@@ -9878,7 +11227,7 @@
         <v>12577237.377249997</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:17">
       <c r="B8" s="38" t="s">
         <v>256</v>
       </c>
@@ -9936,7 +11285,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB3D2433-9FC1-4791-843E-3D32F61D38D2}">
   <dimension ref="B1:L8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="3"/>
     <col min="2" max="2" width="20.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -9949,13 +11298,13 @@
     <col min="11" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" ht="19">
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="L1" s="42"/>
     </row>
-    <row r="2" spans="2:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" ht="16">
       <c r="B2" s="7" t="s">
         <v>57</v>
       </c>
@@ -9965,14 +11314,14 @@
       <c r="F2" s="14"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:12">
       <c r="C3" s="43"/>
       <c r="D3" s="14"/>
       <c r="E3" s="16"/>
       <c r="F3" s="14"/>
       <c r="G3" s="35"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12">
       <c r="B4" s="18" t="s">
         <v>35</v>
       </c>
@@ -10001,7 +11350,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12">
       <c r="B5" s="3" t="s">
         <v>48</v>
       </c>
@@ -10037,7 +11386,7 @@
         <v>149406.91799350994</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:12">
       <c r="B6" s="3" t="s">
         <v>49</v>
       </c>
@@ -10073,7 +11422,7 @@
         <v>80928.747246484549</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="16" thickBot="1">
       <c r="B7" s="3" t="s">
         <v>50</v>
       </c>
@@ -10109,7 +11458,7 @@
         <v>77193.57429664681</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:12">
       <c r="B8" s="45"/>
       <c r="C8" s="45"/>
       <c r="D8" s="45"/>
@@ -10144,7 +11493,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0CBE1E2-E84A-43C8-A74E-07B98D052BDD}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" style="3" customWidth="1"/>
@@ -10163,20 +11512,20 @@
     <col min="23" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="19">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ht="16">
       <c r="A2" s="7" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" ht="16">
       <c r="A3" s="7"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22">
       <c r="A4" s="31" t="s">
         <v>317</v>
       </c>
@@ -10185,7 +11534,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22">
       <c r="A5" s="31" t="s">
         <v>318</v>
       </c>
@@ -10193,7 +11542,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22">
       <c r="A6" s="31" t="s">
         <v>319</v>
       </c>
@@ -10201,11 +11550,11 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22">
       <c r="A7" s="8"/>
       <c r="B7" s="16"/>
     </row>
-    <row r="8" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" s="27" customFormat="1">
       <c r="A8" s="21" t="s">
         <v>61</v>
       </c>
@@ -10273,7 +11622,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22">
       <c r="A9" s="3" t="s">
         <v>79</v>
       </c>
@@ -10356,7 +11705,7 @@
         <v>110093.38168608</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22">
       <c r="A10" s="3" t="s">
         <v>81</v>
       </c>
@@ -10441,7 +11790,7 @@
         <v>498698.55384201225</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" ht="16" thickBot="1">
       <c r="A11" s="3" t="s">
         <v>84</v>
       </c>
@@ -10525,7 +11874,7 @@
         <v>526796.83136789268</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22">
       <c r="A12" s="38" t="s">
         <v>87</v>
       </c>
@@ -10566,12 +11915,12 @@
         <v>1135588.7668959848</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22">
       <c r="A15" s="8" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22">
       <c r="A16" s="18" t="s">
         <v>89</v>
       </c>
@@ -10588,7 +11937,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
         <v>87</v>
       </c>
@@ -10609,7 +11958,7 @@
         <v>1135588.7668959848</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
         <v>90</v>
       </c>
@@ -10630,7 +11979,7 @@
         <v>1025495.385209905</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
         <v>92</v>
       </c>
@@ -10651,7 +12000,7 @@
         <v>0.90305171652321925</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
         <v>91</v>
       </c>
@@ -10672,7 +12021,7 @@
         <v>0.43915418008682272</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
         <v>93</v>
       </c>
